--- a/output/pdf_financials_xlsx/BY.xlsx
+++ b/output/pdf_financials_xlsx/BY.xlsx
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.07628799999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.044503</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.180427</v>
       </c>
     </row>
     <row r="35">
@@ -1010,13 +1010,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.07628799999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.044129</v>
+        <v>0.088632</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.180427</v>
       </c>
     </row>
     <row r="37">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">

--- a/output/pdf_financials_xlsx/BY.xlsx
+++ b/output/pdf_financials_xlsx/BY.xlsx
@@ -2295,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.038678</v>
       </c>
     </row>
     <row r="116">
@@ -3784,7 +3784,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E37" s="5" t="n">
         <v>3.4033</v>
       </c>
@@ -3962,7 +3966,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
